--- a/BECA-Questions-Template.xlsx
+++ b/BECA-Questions-Template.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,45 +27,36 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
       <sz val="14"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-        <bgColor rgb="001F4E78"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -94,20 +85,16 @@
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,13 +461,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -493,7 +478,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Question Types</t>
+          <t>Question Type Codes</t>
         </is>
       </c>
     </row>
@@ -503,7 +488,7 @@
           <t>MCQ</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Multiple Choice Question - Select one or multiple answers</t>
         </is>
@@ -512,10 +497,10 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>TRUE_FALSE</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
+          <t>T/F</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>True/False question - Only two options: True or False</t>
         </is>
@@ -524,219 +509,188 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>FREE_TEXT</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Free text response - Open-ended written answer</t>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Pick List (Dropdown) - Select one from predefined options</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>PICK_LIST</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Dropdown selection - Select one from predefined options</t>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>File Upload with Dataset - Trainee uploads a document with reference data</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>FILE_UPLOAD</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>File upload question - Trainee uploads a document</t>
+          <t>OL</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ordered List (Ranking) - Trainee orders items by priority</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>ORDERED_LIST</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Ranking question - Trainee orders items by priority</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Column Guide</t>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Short Answer - Brief text response</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Essay - Long-form written answer</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Question title (unique identifier)</t>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Supported File Formats</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Question Type</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Type from list above (MCQ, TRUE_FALSE, etc.)</t>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Data Files</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CSV, XLSX, XLS, JSON</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Points</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Numeric points for this question</t>
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Documents</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PDF, DOCX, DOC, TXT</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Category/subject for the question</t>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Images</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>JPG, JPEG, PNG, GIF</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Difficulty</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Level: Easy, Medium, Hard</t>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>AutoCAD</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>.DWG, .DWT (drawing files)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Question Text</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Full question text</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Revit</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>.RVT, .RFA, .RTE, .RFT (building files)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>First option (MCQ only)</t>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Inventor</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>.IAM, .IPT, .IPJ (CAD assemblies)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Second option (MCQ only)</t>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Fusion 360</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>.F3D, .F3Z (design files)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Option C</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Third option (MCQ only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>Option D</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Fourth option (MCQ only)</t>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Archives</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ZIP, RAR (compressed files)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Correct Answer</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Answer: A, B, C, D (MCQ) or True/False (TRUE_FALSE)</t>
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>File Size Limits</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>Image URL</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Optional image/diagram URL for question</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>Dataset File</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Optional filename for dataset file</t>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Maximum file size: 100 MB</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Large files (50MB+) may take longer to upload</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A11:D11"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -748,484 +702,425 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="35" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+    <row r="1" ht="25" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>Question Type</t>
-        </is>
-      </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Type Code</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>Difficulty</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>Question Text</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>Option A</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>Option B</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>Option C</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>Option D</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>Correct Answer</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="L1" s="6" t="inlineStr">
         <is>
           <t>Image URL</t>
         </is>
       </c>
-      <c r="M1" s="5" t="inlineStr">
+      <c r="M1" s="6" t="inlineStr">
         <is>
           <t>Dataset File</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Capital of France</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>MCQ</t>
         </is>
       </c>
-      <c r="C2" s="6" t="n">
+      <c r="C2" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>Geography</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>What is the capital of France?</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>London</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="J2" s="6" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>Madrid</t>
         </is>
       </c>
-      <c r="K2" s="6" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L2" s="6" t="inlineStr"/>
-      <c r="M2" s="6" t="inlineStr"/>
+      <c r="L2" s="7" t="n"/>
+      <c r="M2" s="7" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Python is interpreted</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>TRUE_FALSE</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="n">
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>T/F</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>Programming</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>Python is an interpreted programming language.</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr"/>
-      <c r="H3" s="6" t="inlineStr"/>
-      <c r="I3" s="6" t="inlineStr"/>
-      <c r="J3" s="6" t="inlineStr"/>
-      <c r="K3" s="6" t="inlineStr">
+      <c r="G3" s="7" t="n"/>
+      <c r="H3" s="7" t="n"/>
+      <c r="I3" s="7" t="n"/>
+      <c r="J3" s="7" t="n"/>
+      <c r="K3" s="7" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="L3" s="6" t="inlineStr"/>
-      <c r="M3" s="6" t="inlineStr"/>
+      <c r="L3" s="7" t="n"/>
+      <c r="M3" s="7" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Web Development Language</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Programming</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Which programming language is best for web development?</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>JavaScript</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>C++</t>
+        </is>
+      </c>
+      <c r="K4" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L4" s="7" t="n"/>
+      <c r="M4" s="7" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Describe cloud computing</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>FREE_TEXT</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="n">
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Describe the benefits and drawbacks of cloud computing in your own words.</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr"/>
-      <c r="H4" s="6" t="inlineStr"/>
-      <c r="I4" s="6" t="inlineStr"/>
-      <c r="J4" s="6" t="inlineStr"/>
-      <c r="K4" s="6" t="inlineStr"/>
-      <c r="L4" s="6" t="inlineStr"/>
-      <c r="M4" s="6" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Select programming language</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>PICK_LIST</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Programming</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Which programming language is best for web development?</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>JavaScript</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>C++</t>
-        </is>
-      </c>
-      <c r="K5" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L5" s="6" t="inlineStr"/>
-      <c r="M5" s="6" t="inlineStr"/>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Describe the benefits and drawbacks of cloud computing in your own words. Upload a reference document.</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="n"/>
+      <c r="H5" s="7" t="n"/>
+      <c r="I5" s="7" t="n"/>
+      <c r="J5" s="7" t="n"/>
+      <c r="K5" s="7" t="n"/>
+      <c r="L5" s="7" t="n"/>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>cloud-computing-guide.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Submit your project code</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>FILE_UPLOAD</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Projects</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Order project steps</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>OL</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>Order the following project steps from first to last: Design, Implementation, Testing, Deployment</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>Implementation</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>Testing</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>Deployment</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>1,2,3,4</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="n"/>
+      <c r="M6" s="7" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>CAD Drawing Review</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>Upload your completed project code as a .zip file.</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr"/>
-      <c r="H6" s="6" t="inlineStr"/>
-      <c r="I6" s="6" t="inlineStr"/>
-      <c r="J6" s="6" t="inlineStr"/>
-      <c r="K6" s="6" t="inlineStr"/>
-      <c r="L6" s="6" t="inlineStr"/>
-      <c r="M6" s="6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Order project steps</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>ORDERED_LIST</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>Order the following project steps from first to last:
-1. Design
-2. Implementation
-3. Testing
-4. Deployment</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4</t>
-        </is>
-      </c>
-      <c r="L7" s="6" t="inlineStr"/>
-      <c r="M7" s="6" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>Review the provided AutoCAD drawing and identify all the dimensions. Upload your analysis.</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="n"/>
+      <c r="H7" s="7" t="n"/>
+      <c r="I7" s="7" t="n"/>
+      <c r="J7" s="7" t="n"/>
+      <c r="K7" s="7" t="n"/>
+      <c r="L7" s="7" t="n"/>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>building-plan.dwg</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="n"/>
-      <c r="B8" s="7" t="n"/>
-      <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="n"/>
-      <c r="E8" s="7" t="n"/>
-      <c r="F8" s="7" t="n"/>
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Revit Model Analysis</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>BIM</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>Analyze the Revit model and create a material schedule.</t>
+        </is>
+      </c>
       <c r="G8" s="7" t="n"/>
       <c r="H8" s="7" t="n"/>
       <c r="I8" s="7" t="n"/>
       <c r="J8" s="7" t="n"/>
       <c r="K8" s="7" t="n"/>
       <c r="L8" s="7" t="n"/>
-      <c r="M8" s="7" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n"/>
-      <c r="G9" s="7" t="n"/>
-      <c r="H9" s="7" t="n"/>
-      <c r="I9" s="7" t="n"/>
-      <c r="J9" s="7" t="n"/>
-      <c r="K9" s="7" t="n"/>
-      <c r="L9" s="7" t="n"/>
-      <c r="M9" s="7" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="n"/>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="7" t="n"/>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="7" t="n"/>
-      <c r="I10" s="7" t="n"/>
-      <c r="J10" s="7" t="n"/>
-      <c r="K10" s="7" t="n"/>
-      <c r="L10" s="7" t="n"/>
-      <c r="M10" s="7" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="n"/>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="7" t="n"/>
-      <c r="I11" s="7" t="n"/>
-      <c r="J11" s="7" t="n"/>
-      <c r="K11" s="7" t="n"/>
-      <c r="L11" s="7" t="n"/>
-      <c r="M11" s="7" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="n"/>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n"/>
-      <c r="G12" s="7" t="n"/>
-      <c r="H12" s="7" t="n"/>
-      <c r="I12" s="7" t="n"/>
-      <c r="J12" s="7" t="n"/>
-      <c r="K12" s="7" t="n"/>
-      <c r="L12" s="7" t="n"/>
-      <c r="M12" s="7" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="n"/>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="7" t="n"/>
-      <c r="I13" s="7" t="n"/>
-      <c r="J13" s="7" t="n"/>
-      <c r="K13" s="7" t="n"/>
-      <c r="L13" s="7" t="n"/>
-      <c r="M13" s="7" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="n"/>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
-      <c r="E14" s="7" t="n"/>
-      <c r="F14" s="7" t="n"/>
-      <c r="G14" s="7" t="n"/>
-      <c r="H14" s="7" t="n"/>
-      <c r="I14" s="7" t="n"/>
-      <c r="J14" s="7" t="n"/>
-      <c r="K14" s="7" t="n"/>
-      <c r="L14" s="7" t="n"/>
-      <c r="M14" s="7" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="n"/>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="7" t="n"/>
-      <c r="G15" s="7" t="n"/>
-      <c r="H15" s="7" t="n"/>
-      <c r="I15" s="7" t="n"/>
-      <c r="J15" s="7" t="n"/>
-      <c r="K15" s="7" t="n"/>
-      <c r="L15" s="7" t="n"/>
-      <c r="M15" s="7" t="n"/>
+      <c r="M8" s="7" t="inlineStr">
+        <is>
+          <t>project-model.rvt</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
